--- a/output/pdf_financials_xlsx/WCE.xlsx
+++ b/output/pdf_financials_xlsx/WCE.xlsx
@@ -1007,13 +1007,13 @@
         <v>1.773504</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>3.206648</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>2.44576</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>3.942349</v>
       </c>
     </row>
     <row r="11">
@@ -1106,13 +1106,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000386</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000227</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000151</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -2048,13 +2048,13 @@
         <v>-1.985566</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.355146</v>
+        <v>-1.355532</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.244651</v>
+        <v>-1.244878</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.370076</v>
+        <v>-1.370227</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.730128</v>
@@ -2164,13 +2164,13 @@
         <v>-0.993031</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.287091</v>
+        <v>-1.287477</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.208974</v>
+        <v>-1.209201</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.346648</v>
+        <v>-1.346799</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.721179</v>
@@ -2222,13 +2222,13 @@
         <v>-331.4544823396685</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-957.9492255822089</v>
+        <v>-958.2365156037184</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-722.0772860299827</v>
+        <v>-722.212865077943</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-1170.896443787497</v>
+        <v>-1171.027736718546</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -2452,19 +2452,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.021881</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001871</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.010051</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.005395</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.208923</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.139359</v>
@@ -2491,16 +2491,16 @@
         <v>0.376009</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.468303</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.440569</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.019809</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.019204</v>
       </c>
     </row>
     <row r="35">
@@ -2568,19 +2568,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.021881</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001871</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.010051</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.005395</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.208923</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.139359</v>
@@ -2607,16 +2607,16 @@
         <v>0.376009</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.468303</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.440569</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.019809</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.019204</v>
       </c>
     </row>
     <row r="37">
@@ -3264,19 +3264,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.157391</v>
+        <v>0.13551</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.232886</v>
+        <v>0.231015</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.017699</v>
+        <v>0.007648</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.016763</v>
+        <v>0.011368</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.208923</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.0052</v>
@@ -3303,16 +3303,16 @@
         <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.516597</v>
+        <v>0.048294</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.448606</v>
+        <v>0.008037000000000001</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.038556</v>
+        <v>0.018747</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.074043</v>
+        <v>0.054839</v>
       </c>
     </row>
     <row r="49">
@@ -7756,7 +7756,7 @@
         <v>0</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0078</v>
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>0</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0078</v>
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -26377,7 +26377,11 @@
           <t>Lease payments 7</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -44694,7 +44698,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -44793,7 +44797,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -46191,7 +46195,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -47694,7 +47698,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -50389,7 +50393,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -51686,7 +51690,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -60485,7 +60489,7 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -61598,7 +61602,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -66420,7 +66424,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">

--- a/output/pdf_financials_xlsx/WCE.xlsx
+++ b/output/pdf_financials_xlsx/WCE.xlsx
@@ -2806,31 +2806,31 @@
         <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.022825</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.022825</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.006001</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.001451</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.001372</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.000552</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.003868</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.00023</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>0</v>
@@ -2864,31 +2864,31 @@
         <v>0.047287</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.07989300000000001</v>
+        <v>0.102718</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.036734</v>
+        <v>0.059559</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.013528</v>
+        <v>0.019529</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0.006153</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.015812</v>
+        <v>0.017263</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.109285</v>
+        <v>0.110657</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.190428</v>
+        <v>0.19098</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0.148764</v>
+        <v>0.152632</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.187361</v>
+        <v>0.187591</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>0.041704</v>
@@ -3270,10 +3270,10 @@
         <v>0.231015</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.007648</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.011368</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -3282,19 +3282,19 @@
         <v>0.0052</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.0015</v>
+        <v>4.9e-05</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.01037</v>
+        <v>0.008998000000000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.014762</v>
+        <v>0.01421</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.009560000000000001</v>
+        <v>0.005692</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.01043</v>
+        <v>0.0102</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.006418</v>
@@ -4619,10 +4619,10 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.08121399999999999</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.037579</v>
       </c>
     </row>
     <row r="71">
@@ -4677,10 +4677,10 @@
         <v>0.06</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.08121399999999999</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.037579</v>
       </c>
     </row>
     <row r="72">
@@ -4909,10 +4909,10 @@
         <v>1.735744</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>2.461559</v>
+        <v>2.380345</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>0.796847</v>
+        <v>0.7592680000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5203,12 +5203,10 @@
         <v>0.04167514640131638</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.02245374989991742</v>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07097975762688977</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>0.02897919272524249</v>
       </c>
     </row>
     <row r="81">
@@ -6250,7 +6248,7 @@
         <v>0.432809</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>0.060458</v>
+        <v>0.102089</v>
       </c>
       <c r="P99" s="3" t="n">
         <v>-0.187147</v>
@@ -6871,46 +6869,46 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.037185</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.025183</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.00561</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.004119</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.002547</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.000974</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.00172</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.068799</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.03126</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.0328</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.033046</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.0204</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.033389</v>
       </c>
       <c r="P110" s="3" t="n">
         <v>0</v>
@@ -6931,10 +6929,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.078184</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -7072,7 +7070,7 @@
         <v>0</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>0</v>
+        <v>-1.24</v>
       </c>
       <c r="J113" s="3" t="n">
         <v>0</v>
@@ -8343,10 +8341,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.078184</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.026</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -8403,10 +8401,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.674176</v>
+        <v>-0.75236</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.736626</v>
+        <v>-0.762626</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.344543</v>
@@ -9781,7 +9779,11 @@
           <t>Lease liabilities 7</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -28405,7 +28407,11 @@
           <t>Proceeds from shares issued 11</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -28910,7 +28916,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -29181,7 +29191,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -30111,7 +30125,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -33811,7 +33829,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -34114,7 +34136,11 @@
           <t>Cash paid for acquisition of business</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -38429,7 +38455,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -40762,7 +40792,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E327" s="5" t="n">
         <v>0.037185</v>
       </c>
@@ -43770,7 +43804,11 @@
           <t>Disposition (acquisition) of equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E357" s="5" t="n">
         <v>-0.078184</v>
       </c>
